--- a/fixtures/jeju/timetables/bis/raw/405113.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/405113.xlsx
@@ -6,8 +6,8 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="3008 (한라도서관-터미널-신제주R-노형중흥S)심야" r:id="rId3" sheetId="1"/>
-    <sheet name="3008 (한라대-백록초-용담-공항-외도초-한라대)심야" r:id="rId4" sheetId="2"/>
+    <sheet name="3008 (한라대-백록초-용담-공항-외도초-한라대)심야" r:id="rId3" sheetId="1"/>
+    <sheet name="3008 (한라도서관-터미널-신제주R-노형중흥S)심야" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -18,6 +18,109 @@
     <t>구분</t>
   </si>
   <si>
+    <t>한라대학교</t>
+  </si>
+  <si>
+    <t>백록초</t>
+  </si>
+  <si>
+    <t>한라의료원</t>
+  </si>
+  <si>
+    <t>한라일보</t>
+  </si>
+  <si>
+    <t>용담</t>
+  </si>
+  <si>
+    <t>공항</t>
+  </si>
+  <si>
+    <t>서중</t>
+  </si>
+  <si>
+    <t>외도초</t>
+  </si>
+  <si>
+    <t>도평</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>22:34</t>
+  </si>
+  <si>
+    <t>22:38</t>
+  </si>
+  <si>
+    <t>22:48</t>
+  </si>
+  <si>
+    <t>22:56</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>23:34</t>
+  </si>
+  <si>
+    <t>23:38</t>
+  </si>
+  <si>
+    <t>23:48</t>
+  </si>
+  <si>
+    <t>23:53</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>00:03</t>
+  </si>
+  <si>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>00:13</t>
+  </si>
+  <si>
+    <t>00:18</t>
+  </si>
+  <si>
+    <t>3008번</t>
+  </si>
+  <si>
+    <t>한라대학교-백록초-한라의료원-한라일보-용담-공항-서중-외도초-도평-한라대학교
+*** 토,일,공휴일 운행</t>
+  </si>
+  <si>
+    <t>한라대학교-한라대학교 (심야)</t>
+  </si>
+  <si>
+    <t>첫차 22:30, 막차 23:30, 배차간격 1일 2회, 관광지순환버스(064-746-7310)</t>
+  </si>
+  <si>
+    <t>(시행일: 미입력)</t>
+  </si>
+  <si>
     <t>한라도서관</t>
   </si>
   <si>
@@ -61,12 +164,6 @@
   </si>
   <si>
     <t>22:27</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>3008번</t>
   </si>
   <si>
     <t>한라도서관-제주버스터미널-신제주로터리-제원아파트-한라병원-노형오거리
@@ -77,103 +174,6 @@
   </si>
   <si>
     <t>첫차/막차 22:00, 배차간격 1일 1회, 관광지순환버스(064-746-7310)</t>
-  </si>
-  <si>
-    <t>(시행일: 미입력)</t>
-  </si>
-  <si>
-    <t>한라대학교</t>
-  </si>
-  <si>
-    <t>백록초</t>
-  </si>
-  <si>
-    <t>한라의료원</t>
-  </si>
-  <si>
-    <t>한라일보</t>
-  </si>
-  <si>
-    <t>용담</t>
-  </si>
-  <si>
-    <t>공항</t>
-  </si>
-  <si>
-    <t>서중</t>
-  </si>
-  <si>
-    <t>외도초</t>
-  </si>
-  <si>
-    <t>도평</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>22:34</t>
-  </si>
-  <si>
-    <t>22:38</t>
-  </si>
-  <si>
-    <t>22:48</t>
-  </si>
-  <si>
-    <t>22:56</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>23:34</t>
-  </si>
-  <si>
-    <t>23:38</t>
-  </si>
-  <si>
-    <t>23:48</t>
-  </si>
-  <si>
-    <t>23:53</t>
-  </si>
-  <si>
-    <t>00:03</t>
-  </si>
-  <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>00:13</t>
-  </si>
-  <si>
-    <t>00:18</t>
-  </si>
-  <si>
-    <t>한라대학교-백록초-한라의료원-한라일보-용담-공항-서중-외도초-도평-한라대학교
-*** 토,일,공휴일 운행</t>
-  </si>
-  <si>
-    <t>한라대학교-한라대학교 (심야)</t>
-  </si>
-  <si>
-    <t>첫차 22:30, 막차 23:30, 배차간격 1일 2회, 관광지순환버스(064-746-7310)</t>
   </si>
 </sst>
 </file>
@@ -561,26 +561,30 @@
     <col min="8" max="8" width="14.0" customWidth="true"/>
     <col min="9" max="9" width="14.0" customWidth="true"/>
     <col min="10" max="10" width="14.0" customWidth="true"/>
+    <col min="11" max="11" width="14.0" customWidth="true"/>
+    <col min="12" max="12" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -590,6 +594,8 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" ht="25.0" customHeight="true">
       <c r="B4" s="1"/>
@@ -601,10 +607,12 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -612,10 +620,12 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5"/>
-      <c r="I5" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="I5"/>
       <c r="J5"/>
+      <c r="K5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5"/>
     </row>
     <row r="6" ht="25.0" customHeight="true">
       <c r="B6"/>
@@ -627,6 +637,8 @@
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
     </row>
     <row r="7" ht="40.0" customHeight="true">
       <c r="B7" s="8" t="s">
@@ -653,46 +665,93 @@
       <c r="I7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="9" t="s">
         <v>8</v>
       </c>
+      <c r="K7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="40.0" customHeight="true">
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="11" t="n">
         <v>1.0</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="E8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="G8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="I8" s="12" t="s">
         <v>16</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="40.0" customHeight="true">
+      <c r="B9" s="14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:J4"/>
+    <mergeCell ref="F2:L4"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B5:H6"/>
-    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="B5:J6"/>
+    <mergeCell ref="K5:L6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -712,13 +771,11 @@
     <col min="8" max="8" width="14.0" customWidth="true"/>
     <col min="9" max="9" width="14.0" customWidth="true"/>
     <col min="10" max="10" width="14.0" customWidth="true"/>
-    <col min="11" max="11" width="14.0" customWidth="true"/>
-    <col min="12" max="12" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="17" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -730,8 +787,6 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="18" t="s">
@@ -745,8 +800,6 @@
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
     </row>
     <row r="4" ht="25.0" customHeight="true">
       <c r="B4" s="17"/>
@@ -758,8 +811,6 @@
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="21" t="s">
@@ -771,12 +822,10 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5"/>
-      <c r="I5"/>
+      <c r="I5" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="J5"/>
-      <c r="K5" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5"/>
     </row>
     <row r="6" ht="25.0" customHeight="true">
       <c r="B6"/>
@@ -788,121 +837,72 @@
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
     </row>
     <row r="7" ht="40.0" customHeight="true">
       <c r="B7" s="24" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F7" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="40.0" customHeight="true">
+      <c r="B8" s="30" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="32" t="s">
         <v>25</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="40.0" customHeight="true">
-      <c r="B8" s="27" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" ht="40.0" customHeight="true">
-      <c r="B9" s="30" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:L4"/>
+    <mergeCell ref="F2:J4"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B5:J6"/>
-    <mergeCell ref="K5:L6"/>
+    <mergeCell ref="B5:H6"/>
+    <mergeCell ref="I5:J6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
